--- a/data/trans_orig/Q33-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las horas al día que duerme habitualmente</t>
+          <t>Población según las horas al día que duerme habitualmente (tasa de respuesta: 98,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,42 +716,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,54</t>
+          <t>7,39; 7,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,57</t>
+          <t>7,38; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,63</t>
+          <t>7,45; 7,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>6,98; 7,19</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,08; 7,23</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,94; 7,1</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>6,99; 7,19</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,09; 7,24</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,94; 7,1</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,01; 7,19</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,83; 6,98</t>
+          <t>6,84; 6,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,28</t>
+          <t>7,15; 7,28</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,36</t>
+          <t>7,21; 7,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,05</t>
+          <t>6,92; 7,04</t>
         </is>
       </c>
     </row>
@@ -856,12 +856,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 7,68</t>
+          <t>7,57; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,46</t>
+          <t>7,34; 7,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,05</t>
+          <t>7,19; 7,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,62</t>
+          <t>7,5; 7,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,22 +886,22 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,37</t>
+          <t>7,27; 7,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,7; 7,09</t>
+          <t>6,72; 7,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,56; 7,63</t>
+          <t>7,55; 7,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,29; 7,37</t>
+          <t>7,29; 7,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,53</t>
+          <t>7,04; 7,54</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,51</t>
+          <t>7,36; 7,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,15</t>
+          <t>6,96; 7,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 7,45</t>
+          <t>7,25; 7,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,97; 7,13</t>
+          <t>6,98; 7,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,52</t>
+          <t>7,4; 7,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,36</t>
+          <t>7,2; 7,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,7</t>
+          <t>7,16; 7,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,23</t>
+          <t>7,14; 7,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,3</t>
+          <t>7,21; 7,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,05</t>
+          <t>6,76; 7,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,39</t>
+          <t>7,32; 7,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,36</t>
+          <t>7,04; 7,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q33-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Estudios-trans_orig.xlsx
@@ -663,27 +663,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>7,1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,16</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,02</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>7,09</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>7,16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,02</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,09</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>6,9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,27 +716,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,55</t>
+          <t>7,4; 7,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,38; 7,58</t>
+          <t>7,36; 7,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,63</t>
+          <t>7,44; 7,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,19</t>
+          <t>7,02; 7,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,08; 7,23</t>
+          <t>7,08; 7,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,19</t>
+          <t>7,0; 7,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,84; 6,99</t>
+          <t>6,83; 6,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,04</t>
+          <t>6,92; 7,05</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>7,21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,16</t>
         </is>
       </c>
     </row>
@@ -866,17 +866,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,54</t>
+          <t>7,44; 7,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,98</t>
+          <t>7,16; 7,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,61</t>
+          <t>7,51; 7,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,38</t>
+          <t>7,27; 7,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,72; 7,1</t>
+          <t>7,04; 7,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,37; 7,44</t>
+          <t>7,37; 7,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,54</t>
+          <t>7,12; 7,19</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,07</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,53</t>
+          <t>7,35; 7,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,33</t>
+          <t>7,1; 7,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,4</t>
+          <t>7,21; 7,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,14</t>
+          <t>7,0; 7,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,39; 7,57</t>
+          <t>7,4; 7,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,36</t>
+          <t>7,18; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,13</t>
+          <t>6,98; 7,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,52</t>
+          <t>7,39; 7,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,11</t>
+          <t>7,01; 7,13</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,1</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,44</t>
+          <t>7,35; 7,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,67</t>
+          <t>7,13; 7,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,22</t>
+          <t>7,14; 7,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,12 +1171,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 7,05</t>
+          <t>7,01; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,49</t>
+          <t>7,43; 7,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,39</t>
+          <t>7,33; 7,39</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,35</t>
+          <t>7,08; 7,13</t>
         </is>
       </c>
     </row>
